--- a/erp-server/erp-server-srm/src/main/resources/excel/poReconciliation.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/poReconciliation.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>对账单号</t>
   </si>
@@ -68,6 +68,45 @@
   </si>
   <si>
     <t>收到单据日期</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.cycle}</t>
+  </si>
+  <si>
+    <t>{.settleOrgName}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.supplierConfirmUserName}</t>
+  </si>
+  <si>
+    <t>{.purchaseConfirmUserName}</t>
+  </si>
+  <si>
+    <t>{.reconciliationDate}</t>
+  </si>
+  <si>
+    <t>{.supplierConfirmDate}</t>
+  </si>
+  <si>
+    <t>{.purchaseConfirmDate}</t>
+  </si>
+  <si>
+    <t>{.receiveDate}</t>
   </si>
 </sst>
 </file>
@@ -998,16 +1037,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
-    <col min="6" max="6" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="2" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="26.875" customWidth="1"/>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="13.375" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
     <col min="9" max="9" width="12.125" customWidth="1"/>
     <col min="10" max="10" width="15.75" customWidth="1"/>
     <col min="11" max="11" width="16.125" customWidth="1"/>
@@ -1054,6 +1093,47 @@
       </c>
       <c r="M1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
